--- a/assets/docs/lop4/Hoat dong trai nghiem - Lop 4.xlsx
+++ b/assets/docs/lop4/Hoat dong trai nghiem - Lop 4.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
+          <t>Năng lực số 2.5 CB2a: HS nhận xét bạn bằng lời tích cực, cụ thể và biết cách góp ý tế nhị trên nhóm lớp.</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS nhận xét bạn bằng lời tích cực, cụ thể và biết cách góp ý tế nhị trên nhóm lớp.</t>
+          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS khảo sát, tổng hợp được số liệu về cảnh quan trường lớp và chỉ ra việc cần làm.</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS khảo sát, tổng hợp được số liệu về cảnh quan trường lớp và chỉ ra việc cần làm.
+          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.
 KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí cảnh quan địa phương trên bản đồ số và mô tả đặc điểm của nó.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí cảnh quan địa phương trên bản đồ số và mô tả đặc điểm của nó.</t>
+          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB2a: HS trình bày được sản phẩm giới thiệu nghề truyền thống và nêu rõ nguồn tư liệu.
+          <t>Năng lực số 1.1 CB2c: HS tìm hiểu và trình bày được các công đoạn của một nghề truyền thống, có ghi nguồn tư liệu.
 KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS tìm hiểu và trình bày được các công đoạn của một nghề truyền thống, có ghi nguồn tư liệu.
+          <t>Năng lực số 3.1 CB2a: HS trình bày được sản phẩm giới thiệu nghề truyền thống và nêu rõ nguồn tư liệu.
 KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>

--- a/assets/docs/lop4/Hoat dong trai nghiem - Lop 4.xlsx
+++ b/assets/docs/lop4/Hoat dong trai nghiem - Lop 4.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -604,7 +604,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -841,7 +841,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
